--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
@@ -430,16 +430,16 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>136</v>
+        <v>34</v>
       </c>
       <c r="D2">
-        <v>171</v>
+        <v>377</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="G2">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>426</v>
@@ -450,16 +450,16 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>21</v>
+        <v>134</v>
       </c>
       <c r="D3">
-        <v>324</v>
+        <v>273</v>
       </c>
       <c r="E3">
-        <v>4</v>
+        <v>19</v>
       </c>
       <c r="G3">
-        <v>77</v>
+        <v>0</v>
       </c>
       <c r="H3">
         <v>426</v>

--- a/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
+++ b/debug/excel_overviews/gpt-4.1_vs_Qwen2-7B-Instruct/Llama-3.3-70B-Instruct/simple/total_votes_file.xlsx
@@ -430,13 +430,13 @@
         <v>7</v>
       </c>
       <c r="C2">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D2">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="E2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -450,13 +450,13 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D3">
         <v>273</v>
       </c>
       <c r="E3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G3">
         <v>0</v>
